--- a/tame_output/ON/bt/strategyON_20240302.xlsx
+++ b/tame_output/ON/bt/strategyON_20240302.xlsx
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>402.5%</t>
+          <t>402.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-61.3%</t>
+          <t>-61.4%</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.2%</t>
         </is>
       </c>
     </row>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.325325363243384</v>
+        <v>3.325325363243385</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>1.002982060507059</v>
+        <v>1.001609131620049</v>
       </c>
       <c r="E1890" t="n">
-        <v>3.576687033682281</v>
+        <v>3.576137862127477</v>
       </c>
       <c r="F1890" t="n">
-        <v>2.072345089428422</v>
+        <v>2.069999348272147</v>
       </c>
       <c r="G1890" t="n">
-        <v>4.419257687450258</v>
+        <v>4.417850242756493</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240302.xlsx
+++ b/tame_output/ON/bt/strategyON_20240302.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>402.6%</t>
+          <t>402.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-61.4%</t>
+          <t>-61.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-18.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120.7%</t>
+          <t>120.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
     </row>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.325325363243385</v>
+        <v>3.325325363243384</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>1.001609131620049</v>
+        <v>0.9983367043394793</v>
       </c>
       <c r="E1890" t="n">
-        <v>3.576137862127477</v>
+        <v>3.574828891215249</v>
       </c>
       <c r="F1890" t="n">
-        <v>2.069999348272147</v>
+        <v>2.066418484478444</v>
       </c>
       <c r="G1890" t="n">
-        <v>4.417850242756493</v>
+        <v>4.415701724480271</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240302.xlsx
+++ b/tame_output/ON/bt/strategyON_20240302.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>402.9%</t>
+          <t>425.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-61.7%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-29.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-26.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120.6%</t>
+          <t>118.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199884</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410713</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.325325363243384</v>
+        <v>3.325325363243383</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>0.9983367043394793</v>
+        <v>0.731093657048238</v>
       </c>
       <c r="E1890" t="n">
-        <v>3.574828891215249</v>
+        <v>3.467931672298753</v>
       </c>
       <c r="F1890" t="n">
-        <v>2.066418484478444</v>
+        <v>1.979653824097109</v>
       </c>
       <c r="G1890" t="n">
-        <v>4.415701724480271</v>
+        <v>4.363642928251471</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240302.xlsx
+++ b/tame_output/ON/bt/strategyON_20240302.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,17 +949,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-178.9%</t>
+          <t>-214.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>425.6%</t>
+          <t>505.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-53.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-99.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-86.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-33.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-92.8%</t>
+          <t>-100.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.6%</t>
+          <t>-156.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-27.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>118.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-60.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>111.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-10.6%</t>
         </is>
       </c>
     </row>
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-0.1634063303206248</v>
+        <v>-0.5221239864668332</v>
       </c>
       <c r="E1853" t="n">
-        <v>3.072722650453653</v>
+        <v>2.92923558799517</v>
       </c>
       <c r="F1853" t="n">
-        <v>1.321604620955744</v>
+        <v>1.240991521970754</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.931404379469097</v>
+        <v>3.883036520078103</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-0.1648589967837341</v>
+        <v>-0.5235766529299425</v>
       </c>
       <c r="E1854" t="n">
-        <v>3.073247975912142</v>
+        <v>2.929760913453658</v>
       </c>
       <c r="F1854" t="n">
-        <v>1.320151954492634</v>
+        <v>1.239538855507645</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.931639171634964</v>
+        <v>3.88327131224397</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-0.1652896958323296</v>
+        <v>-0.524007351978538</v>
       </c>
       <c r="E1855" t="n">
-        <v>3.071618235105567</v>
+        <v>2.928131172647083</v>
       </c>
       <c r="F1855" t="n">
-        <v>1.320151954492634</v>
+        <v>1.239538855507645</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.930181710447827</v>
+        <v>3.881813851056833</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-0.1661268728141647</v>
+        <v>-0.5248445289603731</v>
       </c>
       <c r="E1856" t="n">
-        <v>3.073052487767449</v>
+        <v>2.929565425308966</v>
       </c>
       <c r="F1856" t="n">
-        <v>1.319197703230763</v>
+        <v>1.238584604245774</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.93137828314532</v>
+        <v>3.883010423754326</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-0.1776313578124498</v>
+        <v>-0.5363490139586582</v>
       </c>
       <c r="E1857" t="n">
-        <v>3.064556752424393</v>
+        <v>2.921069689965909</v>
       </c>
       <c r="F1857" t="n">
-        <v>1.307693218232478</v>
+        <v>1.227080119247489</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.920581650802607</v>
+        <v>3.872213791411613</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-0.1842922980345976</v>
+        <v>-0.543009954180806</v>
       </c>
       <c r="E1858" t="n">
-        <v>3.063665303035793</v>
+        <v>2.92017824057731</v>
       </c>
       <c r="F1858" t="n">
-        <v>1.307693218232478</v>
+        <v>1.227080119247489</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.922354577502866</v>
+        <v>3.873986718111873</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-0.1864428178148089</v>
+        <v>-0.5451604739610173</v>
       </c>
       <c r="E1859" t="n">
-        <v>3.049137982591113</v>
+        <v>2.90565092013263</v>
       </c>
       <c r="F1859" t="n">
-        <v>1.30604521039388</v>
+        <v>1.225432111408891</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.907698660267112</v>
+        <v>3.859330800876118</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-0.1733805634658412</v>
+        <v>-0.5320982196120496</v>
       </c>
       <c r="E1860" t="n">
-        <v>3.042647659332791</v>
+        <v>2.899160596874307</v>
       </c>
       <c r="F1860" t="n">
-        <v>1.311879757183946</v>
+        <v>1.231266658198957</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.899484163343243</v>
+        <v>3.851116303952249</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-0.1749447145761443</v>
+        <v>-0.5336623707223527</v>
       </c>
       <c r="E1861" t="n">
-        <v>3.040602590544635</v>
+        <v>2.897115528086151</v>
       </c>
       <c r="F1861" t="n">
-        <v>1.311879757183946</v>
+        <v>1.231266658198957</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.898064754999208</v>
+        <v>3.849696895608214</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-0.1728961297144337</v>
+        <v>-0.531613785860642</v>
       </c>
       <c r="E1862" t="n">
-        <v>3.04790958472356</v>
+        <v>2.904422522265077</v>
       </c>
       <c r="F1862" t="n">
-        <v>1.314127457242139</v>
+        <v>1.23351435825715</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.905900935268365</v>
+        <v>3.857533075877371</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-0.1704690651857154</v>
+        <v>-0.5291867213319237</v>
       </c>
       <c r="E1863" t="n">
-        <v>3.048134925540879</v>
+        <v>2.904647863082396</v>
       </c>
       <c r="F1863" t="n">
-        <v>1.313794675434987</v>
+        <v>1.233181576449998</v>
       </c>
       <c r="G1863" t="n">
-        <v>3.904955781189905</v>
+        <v>3.856587921798912</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-0.1717610869600535</v>
+        <v>-0.5304787431062618</v>
       </c>
       <c r="E1864" t="n">
-        <v>3.046379660845903</v>
+        <v>2.90289259838742</v>
       </c>
       <c r="F1864" t="n">
-        <v>1.312502653660649</v>
+        <v>1.23188955467566</v>
       </c>
       <c r="G1864" t="n">
-        <v>3.902942112140061</v>
+        <v>3.854574252749068</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-0.1765756792148949</v>
+        <v>-0.5352933353611031</v>
       </c>
       <c r="E1865" t="n">
-        <v>3.039639256415427</v>
+        <v>2.896152193956944</v>
       </c>
       <c r="F1865" t="n">
-        <v>1.312502653660649</v>
+        <v>1.23188955467566</v>
       </c>
       <c r="G1865" t="n">
-        <v>3.898127544611522</v>
+        <v>3.849759685220528</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-0.173418978184691</v>
+        <v>-0.5321366343308992</v>
       </c>
       <c r="E1866" t="n">
-        <v>3.038895987436386</v>
+        <v>2.895408924977903</v>
       </c>
       <c r="F1866" t="n">
-        <v>1.312502653660649</v>
+        <v>1.23188955467566</v>
       </c>
       <c r="G1866" t="n">
-        <v>3.896121595220399</v>
+        <v>3.847753735829406</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-0.1774320105972128</v>
+        <v>-0.536149666743421</v>
       </c>
       <c r="E1867" t="n">
-        <v>3.047549465140056</v>
+        <v>2.904062402681573</v>
       </c>
       <c r="F1867" t="n">
-        <v>1.312502653660649</v>
+        <v>1.23188955467566</v>
       </c>
       <c r="G1867" t="n">
-        <v>3.906380285889078</v>
+        <v>3.858012426498085</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-0.1911468749223244</v>
+        <v>-0.5498645310685326</v>
       </c>
       <c r="E1868" t="n">
-        <v>3.038163084555707</v>
+        <v>2.894676022097224</v>
       </c>
       <c r="F1868" t="n">
-        <v>1.312502653660649</v>
+        <v>1.23188955467566</v>
       </c>
       <c r="G1868" t="n">
-        <v>3.902479851034773</v>
+        <v>3.85411199164378</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-0.1966637947662908</v>
+        <v>-0.555381450912499</v>
       </c>
       <c r="E1869" t="n">
-        <v>3.034361236673121</v>
+        <v>2.890874174214638</v>
       </c>
       <c r="F1869" t="n">
-        <v>1.312502653660649</v>
+        <v>1.23188955467566</v>
       </c>
       <c r="G1869" t="n">
-        <v>3.900884771089774</v>
+        <v>3.852516911698781</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-0.2014768332316275</v>
+        <v>-0.5601944893778358</v>
       </c>
       <c r="E1870" t="n">
-        <v>3.036214997216195</v>
+        <v>2.892727934757712</v>
       </c>
       <c r="F1870" t="n">
-        <v>1.310956018957863</v>
+        <v>1.230342919972874</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.903735766197311</v>
+        <v>3.855367906806318</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-0.1993596745073347</v>
+        <v>-0.5580773306535429</v>
       </c>
       <c r="E1871" t="n">
-        <v>3.033035556171509</v>
+        <v>2.889548493713026</v>
       </c>
       <c r="F1871" t="n">
-        <v>1.310956018957863</v>
+        <v>1.230342919972874</v>
       </c>
       <c r="G1871" t="n">
-        <v>3.899709461662908</v>
+        <v>3.851341602271915</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-0.1988823279288449</v>
+        <v>-0.5575999840750532</v>
       </c>
       <c r="E1872" t="n">
-        <v>3.03312439348132</v>
+        <v>2.889637331022837</v>
       </c>
       <c r="F1872" t="n">
-        <v>1.310956018957863</v>
+        <v>1.230342919972874</v>
       </c>
       <c r="G1872" t="n">
-        <v>3.899607360341324</v>
+        <v>3.851239500950331</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-0.1978575416219873</v>
+        <v>-0.5565751977681956</v>
       </c>
       <c r="E1873" t="n">
-        <v>3.036105823975494</v>
+        <v>2.89261876151701</v>
       </c>
       <c r="F1873" t="n">
-        <v>1.311980805264721</v>
+        <v>1.231367706279732</v>
       </c>
       <c r="G1873" t="n">
-        <v>3.902793748096869</v>
+        <v>3.854425888705875</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-0.216598921880906</v>
+        <v>-0.5753165780271143</v>
       </c>
       <c r="E1874" t="n">
-        <v>3.033959575169976</v>
+        <v>2.890472512711493</v>
       </c>
       <c r="F1874" t="n">
-        <v>1.311980805264721</v>
+        <v>1.231367706279732</v>
       </c>
       <c r="G1874" t="n">
-        <v>3.908144051394919</v>
+        <v>3.859776192003925</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-0.2295682646660046</v>
+        <v>-0.5882859208122129</v>
       </c>
       <c r="E1875" t="n">
-        <v>3.036687858013114</v>
+        <v>2.893200795554631</v>
       </c>
       <c r="F1875" t="n">
-        <v>1.299011462479622</v>
+        <v>1.218398363494633</v>
       </c>
       <c r="G1875" t="n">
-        <v>3.908278465681037</v>
+        <v>3.859910606290044</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-0.223092117872445</v>
+        <v>-0.5818097740186533</v>
       </c>
       <c r="E1876" t="n">
-        <v>3.042320067352307</v>
+        <v>2.898833004893824</v>
       </c>
       <c r="F1876" t="n">
-        <v>1.305487609273182</v>
+        <v>1.224874510288193</v>
       </c>
       <c r="G1876" t="n">
-        <v>3.915205904378942</v>
+        <v>3.866838044987948</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-0.2194011929160337</v>
+        <v>-0.578118849062242</v>
       </c>
       <c r="E1877" t="n">
-        <v>3.043796437334872</v>
+        <v>2.900309374876388</v>
       </c>
       <c r="F1877" t="n">
-        <v>1.305487609273182</v>
+        <v>1.224874510288193</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.915205904378942</v>
+        <v>3.866838044987948</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-0.2121858400442179</v>
+        <v>-0.5709034961904262</v>
       </c>
       <c r="E1878" t="n">
-        <v>3.05219577560224</v>
+        <v>2.908708713143757</v>
       </c>
       <c r="F1878" t="n">
-        <v>1.375265844563564</v>
+        <v>1.294652745578575</v>
       </c>
       <c r="G1878" t="n">
-        <v>3.962586042671814</v>
+        <v>3.91421818328082</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-0.1611579939623919</v>
+        <v>-0.5198756501086002</v>
       </c>
       <c r="E1879" t="n">
-        <v>3.077089468519407</v>
+        <v>2.933602406060924</v>
       </c>
       <c r="F1879" t="n">
-        <v>1.450475182870665</v>
+        <v>1.369862083885676</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.01219420014051</v>
+        <v>3.963826340749517</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-0.08768816229494347</v>
+        <v>-0.4464058184411517</v>
       </c>
       <c r="E1880" t="n">
-        <v>3.121849102679807</v>
+        <v>2.978362040221324</v>
       </c>
       <c r="F1880" t="n">
-        <v>1.523945014538113</v>
+        <v>1.443331915553124</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.0716478006344</v>
+        <v>4.023279941243406</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-0.007315806831013849</v>
+        <v>-0.3660334629772221</v>
       </c>
       <c r="E1881" t="n">
-        <v>3.168553265612896</v>
+        <v>3.025066203154413</v>
       </c>
       <c r="F1881" t="n">
-        <v>1.604317370002043</v>
+        <v>1.523704271017054</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.134426434660274</v>
+        <v>4.086058575269282</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>0.025616062981837</v>
+        <v>-0.3331015931643713</v>
       </c>
       <c r="E1882" t="n">
-        <v>3.17450684863644</v>
+        <v>3.031019786177957</v>
       </c>
       <c r="F1882" t="n">
-        <v>1.604317370002043</v>
+        <v>1.523704271017054</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.127207269758679</v>
+        <v>4.078839410367685</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>0.00545142143228966</v>
+        <v>-0.3532662347139186</v>
       </c>
       <c r="E1883" t="n">
-        <v>3.159768801242645</v>
+        <v>3.016281738784162</v>
       </c>
       <c r="F1883" t="n">
-        <v>1.584152728452495</v>
+        <v>1.503539629467506</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.108436294054974</v>
+        <v>4.060068434663981</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>0.06411835145382311</v>
+        <v>-0.2945993046923852</v>
       </c>
       <c r="E1884" t="n">
-        <v>3.184351363089815</v>
+        <v>3.040864300631331</v>
       </c>
       <c r="F1884" t="n">
-        <v>1.669112196882633</v>
+        <v>1.588499097897644</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.160527764951613</v>
+        <v>4.112159905560619</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>0.1271875837601626</v>
+        <v>-0.2315300723860456</v>
       </c>
       <c r="E1885" t="n">
-        <v>3.212272784641465</v>
+        <v>3.068785722182982</v>
       </c>
       <c r="F1885" t="n">
-        <v>1.640598634200399</v>
+        <v>1.55998553521541</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.146113355971387</v>
+        <v>4.097745496580393</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>0.1792030977289754</v>
+        <v>-0.1795145584172329</v>
       </c>
       <c r="E1886" t="n">
-        <v>3.237069325915391</v>
+        <v>3.093582263456908</v>
       </c>
       <c r="F1886" t="n">
-        <v>1.640598634200399</v>
+        <v>1.55998553521541</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.150103691657788</v>
+        <v>4.101735832266794</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>0.3547727666498793</v>
+        <v>-0.003944889496328929</v>
       </c>
       <c r="E1887" t="n">
-        <v>3.305821966585011</v>
+        <v>3.162334904126528</v>
       </c>
       <c r="F1887" t="n">
-        <v>1.640598634200399</v>
+        <v>1.55998553521541</v>
       </c>
       <c r="G1887" t="n">
-        <v>4.148628464759046</v>
+        <v>4.100260605368053</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>0.5520421723778774</v>
+        <v>0.1933245162316692</v>
       </c>
       <c r="E1888" t="n">
-        <v>3.399783139041083</v>
+        <v>3.256296076582599</v>
       </c>
       <c r="F1888" t="n">
-        <v>1.837868039928397</v>
+        <v>1.757254940943408</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.282043518360718</v>
+        <v>4.233675658969724</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>0.7511942796149766</v>
+        <v>0.3924766234687684</v>
       </c>
       <c r="E1889" t="n">
-        <v>3.46639284828924</v>
+        <v>3.322905785830756</v>
       </c>
       <c r="F1889" t="n">
-        <v>2.00319056587821</v>
+        <v>1.922577466893221</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.368185900283923</v>
+        <v>4.319818040892929</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.325325363243383</v>
+        <v>3.328369699704814</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>0.731093657048238</v>
+        <v>0.6183217761881794</v>
       </c>
       <c r="E1890" t="n">
-        <v>3.467931672298753</v>
+        <v>3.422822919954729</v>
       </c>
       <c r="F1890" t="n">
-        <v>1.979653824097109</v>
+        <v>1.964504142480385</v>
       </c>
       <c r="G1890" t="n">
-        <v>4.363642928251471</v>
+        <v>4.354553119281436</v>
       </c>
     </row>
   </sheetData>
